--- a/Hardware/Basic/novus_t1200xe_0.8_pa_basic_bom_smd.xlsx
+++ b/Hardware/Basic/novus_t1200xe_0.8_pa_basic_bom_smd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Home\Documents\EAGLE\Toshiba-T1200xe-PSU\jlcpcb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8878D29D-B847-4015-9F1C-52A51C5F21A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55C80596-6D0E-443A-B2DF-5BBAF412B861}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8EE36123-969F-4745-9641-1E84872CB962}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="305">
   <si>
     <t>Value</t>
   </si>
@@ -920,6 +920,21 @@
   </si>
   <si>
     <t>-55℃~+155℃ 1.5kΩ 125mW 150V Thick Film Resistor ±1% ±100ppm/℃ 0805 Chip Resistor - Surface Mount ROHS</t>
+  </si>
+  <si>
+    <t>U8</t>
+  </si>
+  <si>
+    <t>ATMEGA328P</t>
+  </si>
+  <si>
+    <t>TQFP32-08</t>
+  </si>
+  <si>
+    <t>C14877</t>
+  </si>
+  <si>
+    <t>-40℃~+85℃ 1.8V~5.5V 10bit 1KB 20MHz 23 2KB 32KB 8 Bit AVR Built-in FLASH TQFP-32(7x7) Microcontrollers (MCU/MPU/SOC) ROHS</t>
   </si>
 </sst>
 </file>
@@ -1535,10 +1550,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{02ADB103-A702-4238-A390-F1D3834BFC9C}" name="Table1" displayName="Table1" ref="A1:E101" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
-  <autoFilter ref="A1:E101" xr:uid="{02ADB103-A702-4238-A390-F1D3834BFC9C}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E101">
-    <sortCondition ref="A1:A101"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{02ADB103-A702-4238-A390-F1D3834BFC9C}" name="Table1" displayName="Table1" ref="A1:E102" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="A1:E102" xr:uid="{02ADB103-A702-4238-A390-F1D3834BFC9C}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E102">
+    <sortCondition ref="A1:A102"/>
   </sortState>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{5F6A03F2-2887-4A74-BCE8-C7E3614E3EEA}" name="Designator" dataDxfId="4"/>
@@ -1851,7 +1866,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:E102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -3530,52 +3545,69 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>104</v>
+        <v>300</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>105</v>
+        <v>301</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>135</v>
+        <v>302</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>127</v>
+        <v>303</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>128</v>
+        <v>304</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="B102" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="C102" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D101" s="1" t="s">
+      <c r="D102" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="E101" s="1" t="s">
+      <c r="E102" s="1" t="s">
         <v>237</v>
       </c>
     </row>
